--- a/AAII_Financials/Quarterly/PFE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PFE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="92">
   <si>
     <t>PFE</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44654</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44472</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44381</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44290</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44101</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44010</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43919</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43737</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43191</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43009</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42918</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42827</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>15034000</v>
+      </c>
+      <c r="E8" s="3">
         <v>14451000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17557000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16654000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14653000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13715000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17763000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17702000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13283000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14878000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14570000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13492000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13007000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18485000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24290000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22638000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27742000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>25661000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>23635000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24035000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18899000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14516000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11427000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10277000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9864000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>10083000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>10449000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10402000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10363000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13118000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13977000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>13298000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>13466000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12906000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>13703000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>13168000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12896000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>12779000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>13628000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>13045000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3655000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3407000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5065000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3979000</v>
       </c>
-      <c r="G9" s="3">
-        <v>3502000</v>
-      </c>
       <c r="H9" s="3">
+        <v>3501000</v>
+      </c>
+      <c r="I9" s="3">
         <v>2592000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6513000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4873000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2768000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3036000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1066000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8905000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3072000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4747000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9475000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6038000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8625000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9958000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9611000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9965000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7043000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4187000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2732000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1978000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1785000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1914000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2074000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2455000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2550000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2411000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3041000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2672000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2878000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2537000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3064000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2729000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2604000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2441000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3057000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2989000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11379000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11044000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12492000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12675000</v>
       </c>
-      <c r="G10" s="3">
-        <v>11151000</v>
-      </c>
       <c r="H10" s="3">
+        <v>11152000</v>
+      </c>
+      <c r="I10" s="3">
         <v>11123000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11250000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12829000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10515000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11842000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13504000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4587000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9935000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13738000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>14815000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16600000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19117000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>15703000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>14024000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>14070000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11856000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10329000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8695000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8299000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8079000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8169000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8375000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7947000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7813000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>10707000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>10936000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>10626000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>10588000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>10369000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>10639000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>10439000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>10292000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>10338000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>10571000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>10056000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,130 +1219,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2746000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2452000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3323000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2492000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2443000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2179000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3101000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2565000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2676000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2480000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2874000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2682000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2629000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2494000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3615000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2696000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>2816000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>2655000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4565000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6181000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4728000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2010000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3536000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>2296000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1839000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1670000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>2464000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2283000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1842000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1703000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2457000</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2008000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1797000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1743000</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>2311000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1859000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1780000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1708000</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>2512000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1881000</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1451,252 +1467,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4903000</v>
+      </c>
+      <c r="E14" s="3">
         <v>965000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6735000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2208000</v>
       </c>
-      <c r="G14" s="3">
-        <v>782000</v>
-      </c>
       <c r="H14" s="3">
+        <v>907000</v>
+      </c>
+      <c r="I14" s="3">
         <v>1670000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1521000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>389000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2635000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>647000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9496000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1154000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>671000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>975000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1572000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1176000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>380000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>369000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1283000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1189000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>92000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>19000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>824000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1016000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1144000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>246000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3635000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-7109000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>480000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>4210000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>143000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>51000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1619000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>596000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>148000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>228000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>1651000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>2344000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1185000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1183000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1230000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1223000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1211000</v>
       </c>
       <c r="H15" s="3">
         <v>1211000</v>
       </c>
       <c r="I15" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="J15" s="3">
         <v>1359000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1312000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1307000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1308000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1267000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1179000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1184000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1103000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1131000</v>
-      </c>
-      <c r="R15" s="3">
-        <v>822000</v>
       </c>
       <c r="S15" s="3">
         <v>822000</v>
       </c>
       <c r="T15" s="3">
+        <v>822000</v>
+      </c>
+      <c r="U15" s="3">
         <v>835000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>916000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>968000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>917000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>858000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>769000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>862000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>869000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>849000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>995000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1212000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1184000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1183000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>1253000</v>
       </c>
       <c r="AH15" s="3">
         <v>1253000</v>
       </c>
       <c r="AI15" s="3">
+        <v>1253000</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>1191000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>1196000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>1187000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>1177000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>1208000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>1186000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>1122000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>968000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>10843000</v>
+      </c>
+      <c r="E17" s="3">
         <v>9882000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13353000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10779000</v>
       </c>
-      <c r="G17" s="3">
-        <v>10450000</v>
-      </c>
       <c r="H17" s="3">
+        <v>10449000</v>
+      </c>
+      <c r="I17" s="3">
         <v>8892000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15717000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11864000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10310000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10172000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9335000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15878000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10219000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11620000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>19124000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13226000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15640000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15788000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19059000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16383000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>12645000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8989000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10484000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9412000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7346000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6595000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12657000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>959000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8135000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8493000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>14675000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9134000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9000000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8619000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>12545000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9564000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8888000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8552000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>12707000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>9916000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>4191000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4569000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4204000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5875000</v>
       </c>
-      <c r="G18" s="3">
-        <v>4203000</v>
-      </c>
       <c r="H18" s="3">
+        <v>4204000</v>
+      </c>
+      <c r="I18" s="3">
         <v>4823000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2046000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5838000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2973000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4706000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5235000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2386000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2788000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6865000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5166000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9412000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12102000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9873000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4576000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7652000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6254000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5527000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>943000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>865000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2518000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3488000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2208000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9443000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2228000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4625000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-698000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4164000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4466000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4287000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1158000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3604000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4008000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>4227000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>921000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>3129000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2024,618 +2056,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-515000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-36000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1353000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-181000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-121000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-103000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>56000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>67000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-207000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>38000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>52000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-360000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-344000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-218000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>378000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-362000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-501000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-77000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>516000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1011000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>501000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>50000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>875000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-256000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>359000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>408000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>389000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>59000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>122000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>323000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>387000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>150000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>126000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>301000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>119000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>33000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>152000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-1234000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5891000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5788000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6787000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7279000</v>
       </c>
-      <c r="G21" s="3">
-        <v>5535000</v>
-      </c>
       <c r="H21" s="3">
+        <v>5587000</v>
+      </c>
+      <c r="I21" s="3">
         <v>6137000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3349000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7083000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4487000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5976000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6450000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-847000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4316000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8186000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7063000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10495000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12915000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10559000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5776000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9528000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8593000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7254000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1991000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2177000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4644000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4450000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-465000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11404000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4145000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6229000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1065000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6101000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6415000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6004000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2858000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>5471000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>5701000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>5815000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2622000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3291000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>667000</v>
+      </c>
+      <c r="E22" s="3">
         <v>668000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>711000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>652000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>654000</v>
       </c>
       <c r="H22" s="3">
         <v>654000</v>
       </c>
       <c r="I22" s="3">
+        <v>654000</v>
+      </c>
+      <c r="J22" s="3">
         <v>739000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>783000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>778000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>790000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>688000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>695000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>508000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>318000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>313000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>311000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>293000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>322000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>316000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>325000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>316000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>336000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>347000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>345000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>367000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>390000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>415000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>409000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>389000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>361000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>370000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>310000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>326000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>310000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>330000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>320000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>312000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>309000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>297000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>291000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-653000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3169000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1642000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3334000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3044000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2784000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4715000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-103000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3421000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4129000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3352000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2269000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6270000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5231000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9001000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11447000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9050000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4183000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7843000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6949000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5692000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>598000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>570000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3026000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2842000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2264000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9442000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2228000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4323000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-946000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4177000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4527000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4127000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>954000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3585000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3815000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3951000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>776000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1604000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-407000</v>
+      </c>
+      <c r="E24" s="3">
         <v>461000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-216000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>141000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-189000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-421000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>234000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-134000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>293000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-795000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-964000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-71000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>715000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>230000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>356000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1570000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1172000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>334000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-328000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1123000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>808000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-64000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-347000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>422000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>359000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-899000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2866000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1169000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>433000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>232000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>66000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>648000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>556000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-1936000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>727000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>739000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>821000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-71000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>249000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2708000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1640000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3550000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2903000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2973000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>411000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4481000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3128000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3334000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2388000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2340000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5555000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5001000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8645000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9877000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7878000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3849000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8171000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5826000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4884000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>662000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>917000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2604000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2483000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1365000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6576000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3397000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3890000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1178000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4111000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3879000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3571000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2890000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2858000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3076000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3130000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>847000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1355000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2687000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1648000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3541000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2910000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2967000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>410000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4465000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>41000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3115000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3369000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2382000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2327000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5543000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4992000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8629000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9872000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7873000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3851000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8159000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5798000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4875000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>651000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>909000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2595000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2474000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1374000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>6573000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3387000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3884000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1190000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4103000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3872000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3562000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2872000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2840000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>3071000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3121000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>842000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1354000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3122,130 +3179,136 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-13000</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>25000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>7000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-8000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>17000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-5000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-26000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>12000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-2000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>2000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-21000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>34000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-9000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-458000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-13000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-236000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>195000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>560000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>893000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>881000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>1038000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>1111000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>1659000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>796000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>11000</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>9402000</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>2000</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
       <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
         <v>17000</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>515000</v>
+      </c>
+      <c r="E32" s="3">
         <v>36000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1353000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>181000</v>
       </c>
-      <c r="G32" s="3">
-        <v>121000</v>
-      </c>
       <c r="H32" s="3">
+        <v>172000</v>
+      </c>
+      <c r="I32" s="3">
         <v>103000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-56000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-67000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>207000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-38000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-52000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>360000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>344000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>218000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-378000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>362000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>501000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>77000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-516000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1011000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-501000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-50000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-875000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>256000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-359000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-408000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-389000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-59000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-122000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-323000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-387000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-150000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-126000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-301000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-119000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-33000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-152000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>1234000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2687000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1648000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3541000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2910000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2967000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>410000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4465000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>41000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3115000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3369000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2382000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2327000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5543000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4994000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8608000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9906000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7864000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3393000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8146000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5562000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4876000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>846000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1469000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3488000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3355000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-336000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7684000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5046000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3884000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-394000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4114000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3872000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3561000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>12274000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2840000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>3073000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3121000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>859000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1354000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2687000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1648000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3541000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2910000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2967000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>410000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4465000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>41000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3115000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3369000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2382000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2327000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5543000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4994000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8608000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9906000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7864000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3393000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8146000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5562000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4876000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>846000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1469000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3488000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3355000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-336000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7684000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5046000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3884000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-394000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4114000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3872000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3561000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>12274000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2840000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>3073000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3121000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>859000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1354000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44654</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44472</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44381</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44290</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44101</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44010</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43919</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43737</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43191</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43009</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42918</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42827</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4191,1106 +4276,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>976000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1703000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1142000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1343000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1638000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1430000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1043000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1092000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1052000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>719000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2853000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3148000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2632000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2166000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>416000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1298000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1780000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2470000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1944000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1966000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2372000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1768000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1784000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1587000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1801000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2151000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1121000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2785000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1784000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1937000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1139000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3559000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2704000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2302000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1342000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2779000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2585000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4057000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2595000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2094000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>10728000</v>
+      </c>
+      <c r="E42" s="3">
         <v>11378000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>12454000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13643000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11611000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15889000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19434000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8861000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6048000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>11210000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9837000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>41034000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>42153000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17806000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>22316000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>34825000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>31524000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>21427000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>29125000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>27730000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>19328000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>11899000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10437000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8912000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9581000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>8199000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>8525000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>6302000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>11128000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>9682000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>17694000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>13680000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>10727000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>9119000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>18650000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>14146000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>11748000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>10503000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>15255000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>12277000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>16192000</v>
+      </c>
+      <c r="E43" s="3">
         <v>16173000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15841000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>18115000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>16094000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>14745000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14777000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17694000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15087000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15222000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15544000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>15003000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13425000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15445000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14529000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>18620000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>17738000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16342000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>11479000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11897000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>10587000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9864000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7930000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10012000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>9128000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>9881000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6772000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>9439000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9793000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>9599000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8025000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>10024000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9873000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9452000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8221000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>10002000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9476000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>8892000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8225000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9836000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>9945000</v>
+      </c>
+      <c r="E44" s="3">
         <v>10667000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10654000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11468000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11669000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10852000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10851000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>11721000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11447000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10892000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10189000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10204000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10310000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9541000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8981000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9513000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10454000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>9979000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>9059000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8640000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8948000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8493000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8046000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>9295000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>8564000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>8423000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>7068000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>8222000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>8233000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>8029000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>7508000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>8184000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>8074000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>8148000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>7578000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>7925000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>7584000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>7415000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>6783000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>7507000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>3517000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2901000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2807000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2355000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2691000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2945000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4253000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3855000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4191000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4372000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4910000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4623000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4827000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5120000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5017000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6147000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5970000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4202000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8086000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7667000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7579000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7509000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6870000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>17933000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>17350000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6084000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9318000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6711000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>16135000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>16043000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>15560000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>6136000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5925000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5814000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5350000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>5439000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4992000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>5011000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>6091000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>6787000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>41358000</v>
+      </c>
+      <c r="E46" s="3">
         <v>42822000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42898000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>46924000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43703000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45861000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>50358000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>43223000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>37825000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42415000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43333000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>74012000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>73347000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>50078000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>51259000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>70403000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>67466000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>54420000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>59693000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>57900000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>48814000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>39533000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>35067000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>47739000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>46424000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>34738000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>32803000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>33459000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>47073000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>45290000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>49926000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>41583000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>37303000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>34835000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>41141000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>40291000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>36385000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>35878000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>38949000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>38501000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>1460000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1506000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1527000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2056000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2048000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1917000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2108000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10827000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11048000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11524000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15382000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14113000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14945000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14628000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15069000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13888000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>18962000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>20737000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>21526000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>21597000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>20942000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>20228000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>20262000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>19008000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>18720000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>18220000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>20147000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>18722000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2905000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2859000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2767000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6444000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>6595000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>6945000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7015000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7311000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7008000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>7346000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>7116000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>9507000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>19029000</v>
+      </c>
+      <c r="E48" s="3">
         <v>19402000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21530000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>18880000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>18776000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>18347000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20682000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>18541000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>18957000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>18803000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21864000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17862000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17488000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17052000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16274000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15441000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>15244000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>15109000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14882000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14436000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14224000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14011000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>15293000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14403000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14113000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>14040000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14258000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>15007000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14794000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14747000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13385000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14036000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13919000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>13971000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>13865000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>13505000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>13386000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>13238000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>13318000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>13284000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>118472000</v>
+      </c>
+      <c r="E49" s="3">
         <v>123968000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>124995000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>120425000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>121699000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>122420000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>123938000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>128556000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>129685000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>132126000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>132683000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>91751000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>92978000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>93478000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>94745000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>77592000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>78956000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>80027000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>74354000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>75795000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>77190000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>77765000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>78048000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>90829000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>91990000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>92966000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>82139000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>97660000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>86376000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>87526000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>88622000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>100920000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>102420000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>104083000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>104693000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>105799000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>106362000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>107083000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>107097000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>110519000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>10038000</v>
+      </c>
+      <c r="E52" s="3">
         <v>9955000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9810000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9398000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9526000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9941000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9710000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10420000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10811000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11285000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11439000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8933000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13149000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13079000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>19858000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18026000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14662000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13548000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11021000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9460000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8750000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7281000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5559000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7004000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6687000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6372000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>21385000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5598000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5051000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4999000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4722000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4855000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4743000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4778000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5083000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5245000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5417000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5239000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5135000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>6619000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>201131000</v>
+      </c>
+      <c r="E54" s="3">
         <v>207618000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>208160000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>208731000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>206095000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>208028000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>213396000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>219476000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>216193000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>221095000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>226501000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>215021000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>220168000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>195617000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>197205000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>195350000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>195290000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>183841000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>181476000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>179188000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>169920000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>158818000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>154229000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>178983000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>177934000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>166336000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>167594000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>170446000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>156199000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>155421000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>159422000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>167838000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>164980000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>164612000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>171797000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>172151000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>168558000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>168784000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>171615000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>178430000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>4581000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4506000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5240000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5024000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5166000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5240000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5633000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5314000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5106000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5591000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6710000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5338000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6081000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6123000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6809000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6267000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6208000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5506000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5578000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4698000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4327000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4064000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4309000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4141000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3872000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3972000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3887000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3942000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4002000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4156000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4674000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4297000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4196000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3879000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4656000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3480000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3439000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3393000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>4536000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>3476000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>2708000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3891000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3500000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4313000</v>
       </c>
       <c r="G58" s="3">
         <v>4313000</v>
       </c>
       <c r="H58" s="3">
+        <v>4313000</v>
+      </c>
+      <c r="I58" s="3">
         <v>4480000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7330000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9727000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11977000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8249000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10893000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2552000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4000000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4188000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2945000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4040000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5990000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>645000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2241000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3629000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3888000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4352000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2703000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>13363000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>13084000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>16007000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>16195000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>16617000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>10507000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>9410000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8831000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7385000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>11583000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>9010000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>9953000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>9448000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>9514000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>7680000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>10688000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>13633000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>12747000</v>
+      </c>
+      <c r="E59" s="3">
         <v>13672000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15975000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14441000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16464000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15102000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18027000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15467000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16915000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17939000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20967000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15355000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17314000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18710000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>32384000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>34007000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35212000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>33117000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>34852000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>33476000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27449000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18236000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>18908000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16650000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15767000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13911000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>19942000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16415000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17521000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15857000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18353000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17331000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>16377000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14476000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>15818000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>15289000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>14229000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>13791000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>15891000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>17650000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>32646000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34348000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36984000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36596000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37726000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36452000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>42995000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43211000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43819000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40497000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>47794000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31136000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34647000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36562000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>42138000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>44314000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>47410000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39268000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>42671000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>41803000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>35664000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>26652000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>25920000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>34154000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>32723000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>33890000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>37304000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>36974000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>32030000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>29423000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>31858000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>29013000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>32156000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>27365000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30427000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>28217000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>27182000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>24864000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>31115000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>34759000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>60772000</v>
+      </c>
+      <c r="E61" s="3">
         <v>60840000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>64147000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>57625000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>57731000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>57917000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>60088000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>58218000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>57881000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>61653000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>64439000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>61581000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>61674000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31978000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>32884000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32629000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>34294000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>35656000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>36195000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>36250000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>35354000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>35347000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>37133000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>49785000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>50529000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>36281000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>35955000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>36044000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>36168000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>35733000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>32909000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>33652000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28935000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>31831000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>33538000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>34503000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>34191000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>36330000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>31398000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>30437000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>18320000</v>
+      </c>
+      <c r="E62" s="3">
         <v>17630000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15812000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>16790000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>17015000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18743000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>17579000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21258000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22251000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23380000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22173000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21809000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21138000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22595000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>26267000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>25516000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>26117000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>26232000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>25148000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>25168000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>28587000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>27954000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>27703000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>29549000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>30118000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>30827000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>30888000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>32032000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>28077000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>31107000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>30897000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>33509000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>33765000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>34875000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>36176000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>48321000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>48491000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>48844000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>49262000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>49633000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>115639000</v>
+      </c>
+      <c r="E66" s="3">
         <v>117214000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>121385000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>115635000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>117083000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>117391000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>124899000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>126918000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>128218000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>128537000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>137213000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>117817000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>120875000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>94381000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>101545000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>102718000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>108082000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>101417000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>104276000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>103496000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>99878000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>90198000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>90991000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>113724000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>113598000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>101310000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>104450000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>105343000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>96632000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>96615000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>96015000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>96520000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>95202000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>94429000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>100489000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>111381000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>110190000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>110349000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>112071000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>115123000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -7573,52 +7740,55 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>17000</v>
       </c>
       <c r="AD70" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="AE70" s="3">
         <v>18000</v>
       </c>
       <c r="AF70" s="3">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="AG70" s="3">
         <v>19000</v>
       </c>
       <c r="AH70" s="3">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="AI70" s="3">
         <v>20000</v>
       </c>
       <c r="AJ70" s="3">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="AK70" s="3">
         <v>21000</v>
       </c>
       <c r="AL70" s="3">
+        <v>21000</v>
+      </c>
+      <c r="AM70" s="3">
         <v>22000</v>
-      </c>
-      <c r="AM70" s="3">
-        <v>23000</v>
       </c>
       <c r="AN70" s="3">
         <v>23000</v>
       </c>
       <c r="AO70" s="3">
+        <v>23000</v>
+      </c>
+      <c r="AP70" s="3">
         <v>24000</v>
       </c>
-      <c r="AP70" s="3">
+      <c r="AQ70" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>112087000</v>
+      </c>
+      <c r="E72" s="3">
         <v>117238000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>114610000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>121150000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>117609000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>119590000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>116725000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>121059000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>116596000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>121318000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>118353000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>126411000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>128796000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>131102000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>125656000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>122967000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>116608000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>111193000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>103394000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>102252000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>96346000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>95158000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>96770000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>100284000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>100203000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>101000000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>97670000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>100113000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>94440000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>93388000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>89554000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>91995000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>89860000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>89961000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>85291000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>75043000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>74107000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>74847000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>71774000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>72846000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>85190000</v>
+      </c>
+      <c r="E76" s="3">
         <v>90101000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>86476000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>92801000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>88695000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>90338000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>88203000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>92286000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>87700000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>92282000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89014000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>96934000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>99019000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>100970000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>95660000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>92632000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>87208000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>82424000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>77200000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>75692000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>70042000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>68620000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>63238000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>65259000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>64336000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>65009000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>63127000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>65085000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>59549000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>58787000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>63388000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>71298000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>69758000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>70162000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>71287000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>60748000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>58345000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>58412000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>59520000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>63282000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44654</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44472</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44381</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44290</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44101</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44010</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43919</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43737</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43191</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43009</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42918</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42827</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-248000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2687000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1648000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3541000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2910000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2967000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>410000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4465000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>41000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3115000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3369000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2382000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2327000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5543000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4994000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8608000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9906000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7864000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3393000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8146000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5562000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4876000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>846000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1469000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3488000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3355000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-336000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7684000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5046000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3884000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-394000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4114000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3872000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3561000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>12274000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2840000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>3073000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3121000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>859000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1354000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E83" s="3">
         <v>403000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>429000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>435000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>420000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>424000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>399000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>376000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>384000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>366000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>374000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>355000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>347000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>343000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1519000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1183000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1175000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1187000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1277000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1360000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1328000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1226000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1046000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1262000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1251000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1218000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1384000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1553000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1528000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1545000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1641000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1614000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1562000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1567000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1574000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1566000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1574000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1555000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1549000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>1396000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>835000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2615000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5348000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4603000</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="H89" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2335000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6721000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6714000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1781000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1090000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5240000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3456000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1208000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1212000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8582000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5973000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8171000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6541000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5914000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10830000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11297000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4539000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5624000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2091000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3556000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3132000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3769000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4508000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2613000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1697000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4739000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5257000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3848000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1983000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>7073000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4888000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3252000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1589000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>5750000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>4737000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-533000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-436000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-845000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-602000</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-564000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-917000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-651000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-637000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-704000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1044000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-810000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-914000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1139000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1001000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-841000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-751000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-643000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-993000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-624000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-540000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-554000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-785000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-525000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-479000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-463000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-672000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-565000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-479000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-460000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-685000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-547000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-424000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-386000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-700000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-450000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-716000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>461000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-864000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="E94" s="3">
         <v>785000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6146000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2430000</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="H94" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3274000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1623000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2057000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4600000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1732000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10996000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>888000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-25485000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3315000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4410000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-627000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11313000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>567000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2586000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10076000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-8137000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1747000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>8330000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>481000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-13011000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-71000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2833000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6760000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1902000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>7550000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-764000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2904000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1474000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>9667000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4778000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2996000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1738000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>4772000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3107000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-4381000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -10194,28 +10426,29 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>2445000</v>
+        <v>2451000</v>
       </c>
       <c r="E96" s="3">
         <v>2445000</v>
       </c>
       <c r="F96" s="3">
+        <v>2445000</v>
+      </c>
+      <c r="G96" s="3">
         <v>2444000</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="H96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2437000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>2380000</v>
       </c>
       <c r="J96" s="3">
         <v>2380000</v>
@@ -10224,100 +10457,103 @@
         <v>2380000</v>
       </c>
       <c r="L96" s="3">
+        <v>2380000</v>
+      </c>
+      <c r="M96" s="3">
         <v>2372000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>2315000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>2314000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>2315000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>2303000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-2245000</v>
       </c>
       <c r="R96" s="3">
         <v>-2245000</v>
       </c>
       <c r="S96" s="3">
+        <v>-2245000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2244000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2249000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2189000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2185000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2183000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2172000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-2112000</v>
       </c>
       <c r="Z96" s="3">
         <v>-2112000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-2112000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-2111000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-2105000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1991000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-2004000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-2002000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-2045000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1963000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1994000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1989000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-2032000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1909000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1895000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1910000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1945000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-1821000</v>
       </c>
       <c r="AP96" s="3">
         <v>-1821000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-1821000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-3663000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2856000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>596000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2477000</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="H100" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5227000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5114000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4636000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2459000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4931000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5442000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3779000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>27174000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2771000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5015000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5761000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2520000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6578000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3351000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1101000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2557000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2807000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-13787000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2821000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9159000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2200000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2440000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3273000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-851000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-8467000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6407000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1406000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1908000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-10720000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1711000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2989000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-4907000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2228000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1624000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-29000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-18000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-28000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-32000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-26000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-72000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-66000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-26000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-72000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-66000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-27000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-37000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5000</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="Z101" s="3">
         <v>31000</v>
       </c>
       <c r="AA101" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>9000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>12000</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-101000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>55000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-14000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>30000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>16000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>21000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-136000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-726000</v>
+      </c>
+      <c r="E102" s="3">
         <v>563000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-197000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-302000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>375000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-45000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>342000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2137000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-315000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>533000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>476000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1754000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-869000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-487000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-688000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>529000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-50000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-384000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>608000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>198000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-218000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-351000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>846000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1495000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1008000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-180000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>792000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2432000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>846000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>396000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>985000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1428000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>198000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1470000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1465000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>501000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1317000</v>
       </c>
     </row>
